--- a/data/Flass/CL31-FL-March.xlsx
+++ b/data/Flass/CL31-FL-March.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://murphygroup-my.sharepoint.com/personal/rhyskift_murphygroup_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C84183FB-CC14-4EE8-8991-7F05A33BCA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D8E4B2-31EC-481A-8515-433D490E73F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19845" yWindow="2025" windowWidth="18180" windowHeight="9855" xr2:uid="{84CA8325-49DA-4E7D-9057-7D370EB309AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84CA8325-49DA-4E7D-9057-7D370EB309AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -446,7 +446,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -454,13 +454,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,41 +812,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310D42E8-0C57-4A55-B741-FE87DF94B6A4}">
   <dimension ref="A1:J66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -856,7 +881,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -882,7 +907,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -905,7 +930,7 @@
         <v>-111</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -931,7 +956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -954,7 +979,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -977,7 +1002,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1006,7 +1031,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1032,7 +1057,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1058,7 +1083,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1087,7 +1112,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1113,7 +1138,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1145,7 +1170,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1168,7 +1193,7 @@
         <v>-111</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1191,7 +1216,7 @@
         <v>-111</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1214,7 +1239,7 @@
         <v>-111</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1240,7 +1265,7 @@
         <v>-96</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -1269,7 +1294,7 @@
         <v>-133</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -1298,7 +1323,7 @@
         <v>-129</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1327,7 +1352,7 @@
         <v>-121</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -1356,7 +1381,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1385,7 +1410,7 @@
         <v>-96</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1414,7 +1439,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1443,7 +1468,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1469,7 +1494,7 @@
         <v>-131</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -1495,7 +1520,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -1521,7 +1546,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -1553,7 +1578,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1579,7 +1604,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1605,7 +1630,7 @@
         <v>-131</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1628,7 +1653,7 @@
         <v>-131</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1657,7 +1682,7 @@
         <v>-131</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1686,7 +1711,7 @@
         <v>-131</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1709,7 +1734,7 @@
         <v>-131</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1735,7 +1760,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1764,7 +1789,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1793,7 +1818,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1816,7 +1841,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1842,7 +1867,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -1868,7 +1893,7 @@
         <v>-115</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -1891,7 +1916,7 @@
         <v>-115</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -1914,7 +1939,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -1943,7 +1968,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -1966,7 +1991,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -1995,7 +2020,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2018,7 +2043,7 @@
         <v>-127</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2044,7 +2069,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -2070,7 +2095,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>95</v>
       </c>
@@ -2099,7 +2124,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -2125,7 +2150,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -2154,7 +2179,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -2183,7 +2208,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>102</v>
       </c>
@@ -2212,7 +2237,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2241,7 +2266,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -2270,7 +2295,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -2299,7 +2324,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -2328,7 +2353,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -2357,7 +2382,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -2386,7 +2411,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -2415,7 +2440,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -2444,7 +2469,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>120</v>
       </c>
@@ -2473,7 +2498,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>122</v>
       </c>
@@ -2502,7 +2527,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -2531,7 +2556,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -2557,7 +2582,7 @@
         <v>-136</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>127</v>
       </c>

--- a/data/Flass/CL31-FL-March.xlsx
+++ b/data/Flass/CL31-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBA3103-F013-40B2-88A5-3ED161911800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D2A755-4569-4ED0-8E71-8EEAD3C18790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Flass/CL31-FL-March.xlsx
+++ b/data/Flass/CL31-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D2A755-4569-4ED0-8E71-8EEAD3C18790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AF45B7-6112-41C9-90BD-BBAC8087C0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,7 +370,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -378,11 +378,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -392,6 +407,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -743,37 +761,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>2</v>
       </c>
     </row>

--- a/data/Flass/CL31-FL-March.xlsx
+++ b/data/Flass/CL31-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AF45B7-6112-41C9-90BD-BBAC8087C0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFF58EE-0C17-4E13-AF23-674B1B9749CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>Activity Name</t>
   </si>
   <si>
-    <t>Primary Constraint</t>
-  </si>
-  <si>
     <t>AMP8-FLL-UU-1750</t>
   </si>
   <si>
@@ -346,7 +343,10 @@
     <t>Remaining Duration</t>
   </si>
   <si>
-    <t>Variance - BL Project Finish Date</t>
+    <t>Variance - BL Finish Date</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
 </sst>
 </file>
@@ -370,7 +370,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -378,26 +378,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -407,9 +392,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -751,1203 +733,1203 @@
   <cols>
     <col min="1" max="1" width="28.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="31.28515625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25" style="3" customWidth="1"/>
-    <col min="4" max="7" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="40.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="2" customWidth="1"/>
+    <col min="3" max="6" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="40.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25" style="3" customWidth="1"/>
     <col min="11" max="11" width="25.42578125" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="19.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4">
+        <v>46143.333333333299</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46164.708333333299</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46143.333333333299</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46164.708333333299</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46143.333333333299</v>
-      </c>
-      <c r="E2" s="4">
-        <v>46164.708333333299</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4">
-        <v>46143.333333333299</v>
-      </c>
-      <c r="H2" s="4">
-        <v>46164.708333333299</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4">
+        <v>46168.333333333299</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46168.333333333299</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46168.333333333299</v>
-      </c>
-      <c r="E3" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46168.333333333299</v>
-      </c>
-      <c r="H3" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46142.708333333299</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46142.708333333299</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E4" s="4">
-        <v>46142.708333333299</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H4" s="4">
-        <v>46142.708333333299</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E5" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H5" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="K5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
+      <c r="C6" s="4">
+        <v>46129.333333333299</v>
       </c>
       <c r="D6" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4">
         <v>46129.333333333299</v>
       </c>
-      <c r="E6" s="4">
+      <c r="G6" s="4">
         <v>46174.708333333299</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H6" s="4">
-        <v>46174.708333333299</v>
+      <c r="H6" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E7" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H7" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E8" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H8" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46157.708333333299</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46157.708333333299</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E9" s="4">
-        <v>46157.708333333299</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H9" s="4">
-        <v>46157.708333333299</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46164.708333333299</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46129.333333333299</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46164.708333333299</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="E10" s="4">
-        <v>46164.708333333299</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H10" s="4">
-        <v>46164.708333333299</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
+      <c r="C11" s="4">
+        <v>46113.333333333299</v>
       </c>
       <c r="D11" s="4">
+        <v>46128.708333333299</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4">
         <v>46113.333333333299</v>
       </c>
-      <c r="E11" s="4">
+      <c r="G11" s="4">
         <v>46128.708333333299</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46113.333333333299</v>
-      </c>
-      <c r="H11" s="4">
-        <v>46128.708333333299</v>
+      <c r="H11" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>6</v>
+      <c r="C12" s="4">
+        <v>46246.333333333299</v>
       </c>
       <c r="D12" s="4">
         <v>46246.333333333299</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4">
         <v>46246.333333333299</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="G12" s="4">
         <v>46246.333333333299</v>
       </c>
-      <c r="H12" s="4">
-        <v>46246.333333333299</v>
+      <c r="H12" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>12</v>
+      <c r="C13" s="4">
+        <v>46160.333333333299</v>
       </c>
       <c r="D13" s="4">
+        <v>46164.708333333299</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4">
         <v>46160.333333333299</v>
       </c>
-      <c r="E13" s="4">
+      <c r="G13" s="4">
         <v>46164.708333333299</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46160.333333333299</v>
-      </c>
-      <c r="H13" s="4">
-        <v>46164.708333333299</v>
+      <c r="H13" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>15</v>
+      <c r="C14" s="4">
+        <v>46143.333333333299</v>
       </c>
       <c r="D14" s="4">
+        <v>46157.708333333299</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="4">
         <v>46143.333333333299</v>
       </c>
-      <c r="E14" s="4">
+      <c r="G14" s="4">
         <v>46157.708333333299</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46143.333333333299</v>
-      </c>
-      <c r="H14" s="4">
-        <v>46157.708333333299</v>
+      <c r="H14" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>34</v>
+      <c r="C15" s="4">
+        <v>46129.333333333299</v>
       </c>
       <c r="D15" s="4">
+        <v>46164.708333333299</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="4">
         <v>46129.333333333299</v>
       </c>
-      <c r="E15" s="4">
+      <c r="G15" s="4">
         <v>46164.708333333299</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H15" s="4">
-        <v>46164.708333333299</v>
+      <c r="H15" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>34</v>
+      <c r="C16" s="4">
+        <v>46129.333333333299</v>
       </c>
       <c r="D16" s="4">
+        <v>46164.708333333299</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4">
         <v>46129.333333333299</v>
       </c>
-      <c r="E16" s="4">
+      <c r="G16" s="4">
         <v>46164.708333333299</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H16" s="4">
-        <v>46164.708333333299</v>
+      <c r="H16" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="4">
+        <v>46170.333333333299</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46245.708333333299</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46170.333333333299</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46245.708333333299</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="4">
-        <v>46170.333333333299</v>
-      </c>
-      <c r="E17" s="4">
-        <v>46245.708333333299</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46170.333333333299</v>
-      </c>
-      <c r="H17" s="4">
-        <v>46245.708333333299</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>12</v>
+      <c r="C18" s="4">
+        <v>46178.333333333299</v>
       </c>
       <c r="D18" s="4">
+        <v>46184.708333333299</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="4">
         <v>46178.333333333299</v>
       </c>
-      <c r="E18" s="4">
+      <c r="G18" s="4">
         <v>46184.708333333299</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="4">
-        <v>46178.333333333299</v>
-      </c>
-      <c r="H18" s="4">
-        <v>46184.708333333299</v>
+      <c r="H18" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="4">
+        <v>46170.333333333299</v>
+      </c>
+      <c r="D19" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46170.333333333299</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="4">
-        <v>46170.333333333299</v>
-      </c>
-      <c r="E19" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46170.333333333299</v>
-      </c>
-      <c r="H19" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="4">
+        <v>46233.333333333299</v>
+      </c>
+      <c r="D20" s="4">
+        <v>46245.708333333299</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46233.333333333299</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46245.708333333299</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="4">
-        <v>46233.333333333299</v>
-      </c>
-      <c r="E20" s="4">
-        <v>46245.708333333299</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="4">
-        <v>46233.333333333299</v>
-      </c>
-      <c r="H20" s="4">
-        <v>46245.708333333299</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="4">
+        <v>46232.333333333299</v>
+      </c>
+      <c r="D21" s="4">
+        <v>46232.708333333299</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46232.333333333299</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46232.708333333299</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="4">
-        <v>46232.333333333299</v>
-      </c>
-      <c r="E21" s="4">
-        <v>46232.708333333299</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="4">
-        <v>46232.333333333299</v>
-      </c>
-      <c r="H21" s="4">
-        <v>46232.708333333299</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="4">
+        <v>46231.333333333299</v>
+      </c>
+      <c r="D22" s="4">
+        <v>46232.708333333299</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4">
+        <v>46231.333333333299</v>
+      </c>
+      <c r="G22" s="4">
+        <v>46232.708333333299</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="4">
-        <v>46231.333333333299</v>
-      </c>
-      <c r="E22" s="4">
-        <v>46232.708333333299</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="4">
-        <v>46231.333333333299</v>
-      </c>
-      <c r="H22" s="4">
-        <v>46232.708333333299</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>12</v>
+      <c r="C23" s="4">
+        <v>46224.333333333299</v>
       </c>
       <c r="D23" s="4">
+        <v>46230.708333333299</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="4">
         <v>46224.333333333299</v>
       </c>
-      <c r="E23" s="4">
+      <c r="G23" s="4">
         <v>46230.708333333299</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46224.333333333299</v>
-      </c>
-      <c r="H23" s="4">
-        <v>46230.708333333299</v>
+      <c r="H23" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
+      <c r="C24" s="4">
+        <v>46210.333333333299</v>
       </c>
       <c r="D24" s="4">
+        <v>46230.708333333299</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="4">
         <v>46210.333333333299</v>
       </c>
-      <c r="E24" s="4">
+      <c r="G24" s="4">
         <v>46230.708333333299</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="4">
-        <v>46210.333333333299</v>
-      </c>
-      <c r="H24" s="4">
-        <v>46230.708333333299</v>
+      <c r="H24" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>12</v>
+      <c r="C25" s="4">
+        <v>46203.333333333299</v>
       </c>
       <c r="D25" s="4">
+        <v>46209.708333333299</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4">
         <v>46203.333333333299</v>
       </c>
-      <c r="E25" s="4">
+      <c r="G25" s="4">
         <v>46209.708333333299</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="4">
-        <v>46203.333333333299</v>
-      </c>
-      <c r="H25" s="4">
-        <v>46209.708333333299</v>
+      <c r="H25" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>12</v>
+      <c r="C26" s="4">
+        <v>46196.333333333299</v>
       </c>
       <c r="D26" s="4">
+        <v>46202.708333333299</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="4">
         <v>46196.333333333299</v>
       </c>
-      <c r="E26" s="4">
+      <c r="G26" s="4">
         <v>46202.708333333299</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="4">
-        <v>46196.333333333299</v>
-      </c>
-      <c r="H26" s="4">
-        <v>46202.708333333299</v>
+      <c r="H26" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>30</v>
+      <c r="C27" s="4">
+        <v>46196.333333333299</v>
       </c>
       <c r="D27" s="4">
+        <v>46223.708333333299</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="4">
         <v>46196.333333333299</v>
       </c>
-      <c r="E27" s="4">
+      <c r="G27" s="4">
         <v>46223.708333333299</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="4">
-        <v>46196.333333333299</v>
-      </c>
-      <c r="H27" s="4">
-        <v>46223.708333333299</v>
+      <c r="H27" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>64</v>
+      <c r="C28" s="4">
+        <v>46176.333333333299</v>
       </c>
       <c r="D28" s="4">
+        <v>46177.708333333299</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="4">
         <v>46176.333333333299</v>
       </c>
-      <c r="E28" s="4">
+      <c r="G28" s="4">
         <v>46177.708333333299</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="4">
-        <v>46176.333333333299</v>
-      </c>
-      <c r="H28" s="4">
-        <v>46177.708333333299</v>
+      <c r="H28" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="4">
+        <v>46185.333333333299</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46195.708333333299</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46185.333333333299</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46195.708333333299</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="4">
-        <v>46185.333333333299</v>
-      </c>
-      <c r="E29" s="4">
-        <v>46195.708333333299</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="4">
-        <v>46185.333333333299</v>
-      </c>
-      <c r="H29" s="4">
-        <v>46195.708333333299</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="K29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>12</v>
+      <c r="C30" s="4">
+        <v>46168.333333333299</v>
       </c>
       <c r="D30" s="4">
+        <v>46174.708333333299</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="4">
         <v>46168.333333333299</v>
       </c>
-      <c r="E30" s="4">
+      <c r="G30" s="4">
         <v>46174.708333333299</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="4">
-        <v>46168.333333333299</v>
-      </c>
-      <c r="H30" s="4">
-        <v>46174.708333333299</v>
+      <c r="H30" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>61</v>
+      <c r="C31" s="4">
+        <v>46175.333333333299</v>
       </c>
       <c r="D31" s="4">
+        <v>46175.708333333299</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4">
         <v>46175.333333333299</v>
       </c>
-      <c r="E31" s="4">
+      <c r="G31" s="4">
         <v>46175.708333333299</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="4">
-        <v>46175.333333333299</v>
-      </c>
-      <c r="H31" s="4">
-        <v>46175.708333333299</v>
+      <c r="H31" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="4">
+        <v>46160.333333333299</v>
+      </c>
+      <c r="D32" s="4">
+        <v>46163.708333333299</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="4">
+        <v>46160.333333333299</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46163.708333333299</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="4">
-        <v>46160.333333333299</v>
-      </c>
-      <c r="E32" s="4">
-        <v>46163.708333333299</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="4">
-        <v>46160.333333333299</v>
-      </c>
-      <c r="H32" s="4">
-        <v>46163.708333333299</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="K32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>30</v>
+      <c r="C33" s="4">
+        <v>46129.333333333299</v>
       </c>
       <c r="D33" s="4">
+        <v>46157.708333333299</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="4">
         <v>46129.333333333299</v>
       </c>
-      <c r="E33" s="4">
+      <c r="G33" s="4">
         <v>46157.708333333299</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="4">
-        <v>46129.333333333299</v>
-      </c>
-      <c r="H33" s="4">
-        <v>46157.708333333299</v>
+      <c r="H33" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="4">
+      <c r="C34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="4">
         <v>46128.708333333299</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="4">
+      <c r="E34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="4">
         <v>46128.708333333299</v>
       </c>
+      <c r="H34" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="I34" s="2" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1965,17 +1947,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/Flass/CL31-FL-March.xlsx
+++ b/data/Flass/CL31-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFF58EE-0C17-4E13-AF23-674B1B9749CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E892480-7DE5-4900-91FD-BD4C57B20BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,12 +334,6 @@
     <t xml:space="preserve">Total Float </t>
   </si>
   <si>
-    <t>BL1 Start</t>
-  </si>
-  <si>
-    <t>BL1 Finish</t>
-  </si>
-  <si>
     <t>Remaining Duration</t>
   </si>
   <si>
@@ -347,6 +341,12 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>BL Project Finish</t>
+  </si>
+  <si>
+    <t>BL Project Start</t>
   </si>
 </sst>
 </file>
@@ -759,22 +759,22 @@
         <v>96</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>97</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="19.5" customHeight="1">

--- a/data/Flass/CL31-FL-March.xlsx
+++ b/data/Flass/CL31-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E892480-7DE5-4900-91FD-BD4C57B20BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB297F6-819A-4E83-95B2-0CDA5F9B6E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,10 +343,10 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>BL Project Finish</t>
-  </si>
-  <si>
-    <t>BL Project Start</t>
+    <t>BL1 Start</t>
+  </si>
+  <si>
+    <t>BL1 Finish</t>
   </si>
 </sst>
 </file>
@@ -759,10 +759,10 @@
         <v>96</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>99</v>

--- a/data/Flass/CL31-FL-March.xlsx
+++ b/data/Flass/CL31-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB297F6-819A-4E83-95B2-0CDA5F9B6E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6757B2-E3EA-4A3F-9A86-FDCF59A6788C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,10 +343,10 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>BL1 Start</t>
-  </si>
-  <si>
-    <t>BL1 Finish</t>
+    <t>BL Project Finish</t>
+  </si>
+  <si>
+    <t>BL Project Start</t>
   </si>
 </sst>
 </file>
@@ -759,10 +759,10 @@
         <v>96</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>99</v>
